--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -464,7 +464,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-schedule|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-schedule|2.2.0</t>
   </si>
   <si>
     <t>Schedule.meta.security</t>
@@ -632,7 +632,7 @@
     <t>serviceTypeDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.2.0}
 </t>
   </si>
   <si>
@@ -654,7 +654,7 @@
     <t>availabilityTime</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-schedule-availability-time|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-schedule-availability-time|2.2.0}
 </t>
   </si>
   <si>
@@ -766,13 +766,13 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
   </si>
   <si>
     <t>Schedule.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.2.0-ballot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.2.0-ballot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0-ballot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0-ballot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0-ballot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(Device|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0)
 </t>
   </si>
   <si>
@@ -1157,7 +1157,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.7421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.19921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
